--- a/artfynd/A 34151-2019 artfynd.xlsx
+++ b/artfynd/A 34151-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34151-2019 artfynd.xlsx
+++ b/artfynd/A 34151-2019 artfynd.xlsx
@@ -7559,7 +7559,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118024123</v>
+        <v>118024127</v>
       </c>
       <c r="B57" t="n">
         <v>97836</v>
@@ -7593,24 +7593,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bråtarna, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609012</v>
+        <v>609051</v>
       </c>
       <c r="R57" t="n">
-        <v>6574164</v>
+        <v>6574160</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7642,7 +7634,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7652,7 +7644,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7661,7 +7653,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7801,7 +7792,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118024125</v>
+        <v>118024123</v>
       </c>
       <c r="B59" t="n">
         <v>97836</v>
@@ -7849,10 +7840,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609039</v>
+        <v>609012</v>
       </c>
       <c r="R59" t="n">
-        <v>6574166</v>
+        <v>6574164</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7884,7 +7875,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7894,7 +7885,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8043,7 +8034,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118024128</v>
+        <v>118024126</v>
       </c>
       <c r="B61" t="n">
         <v>97836</v>
@@ -8091,10 +8082,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609052</v>
+        <v>609043</v>
       </c>
       <c r="R61" t="n">
-        <v>6574161</v>
+        <v>6574157</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8126,7 +8117,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8136,7 +8127,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8164,7 +8155,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118024126</v>
+        <v>118024128</v>
       </c>
       <c r="B62" t="n">
         <v>97836</v>
@@ -8212,10 +8203,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609043</v>
+        <v>609052</v>
       </c>
       <c r="R62" t="n">
-        <v>6574157</v>
+        <v>6574161</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8247,7 +8238,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8257,7 +8248,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8285,7 +8276,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118024127</v>
+        <v>118024125</v>
       </c>
       <c r="B63" t="n">
         <v>97836</v>
@@ -8319,16 +8310,24 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bråtarna, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609051</v>
+        <v>609039</v>
       </c>
       <c r="R63" t="n">
-        <v>6574160</v>
+        <v>6574166</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8360,7 +8359,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8370,7 +8369,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8379,6 +8378,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34151-2019 artfynd.xlsx
+++ b/artfynd/A 34151-2019 artfynd.xlsx
@@ -7559,10 +7559,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118024127</v>
+        <v>118024123</v>
       </c>
       <c r="B57" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7593,16 +7593,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Bråtarna, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609051</v>
+        <v>609012</v>
       </c>
       <c r="R57" t="n">
-        <v>6574160</v>
+        <v>6574164</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7634,7 +7642,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7644,7 +7652,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7653,6 +7661,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7671,10 +7680,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118024124</v>
+        <v>118024125</v>
       </c>
       <c r="B58" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7719,10 +7728,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>609041</v>
+        <v>609039</v>
       </c>
       <c r="R58" t="n">
-        <v>6574167</v>
+        <v>6574166</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7792,10 +7801,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118024123</v>
+        <v>118024124</v>
       </c>
       <c r="B59" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7840,10 +7849,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609012</v>
+        <v>609041</v>
       </c>
       <c r="R59" t="n">
-        <v>6574164</v>
+        <v>6574167</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7875,7 +7884,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7885,7 +7894,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7916,7 +7925,7 @@
         <v>118024122</v>
       </c>
       <c r="B60" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8034,10 +8043,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118024126</v>
+        <v>118024128</v>
       </c>
       <c r="B61" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8082,10 +8091,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609043</v>
+        <v>609052</v>
       </c>
       <c r="R61" t="n">
-        <v>6574157</v>
+        <v>6574161</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8117,7 +8126,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8127,7 +8136,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8155,10 +8164,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118024128</v>
+        <v>118024126</v>
       </c>
       <c r="B62" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8203,10 +8212,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609052</v>
+        <v>609043</v>
       </c>
       <c r="R62" t="n">
-        <v>6574161</v>
+        <v>6574157</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8238,7 +8247,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8248,7 +8257,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8276,10 +8285,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118024125</v>
+        <v>118024127</v>
       </c>
       <c r="B63" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8310,24 +8319,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bråtarna, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609039</v>
+        <v>609051</v>
       </c>
       <c r="R63" t="n">
-        <v>6574166</v>
+        <v>6574160</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8359,7 +8360,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8369,7 +8370,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8378,7 +8379,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34151-2019 artfynd.xlsx
+++ b/artfynd/A 34151-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8509,6 +8509,129 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121864880</v>
+      </c>
+      <c r="B65" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Bråtarna 6, Srm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>609010</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6574278</v>
+      </c>
+      <c r="S65" t="n">
+        <v>50</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Länna</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34151-2019 artfynd.xlsx
+++ b/artfynd/A 34151-2019 artfynd.xlsx
@@ -8399,7 +8399,7 @@
         <v>121864880</v>
       </c>
       <c r="B64" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>

--- a/artfynd/A 34151-2019 artfynd.xlsx
+++ b/artfynd/A 34151-2019 artfynd.xlsx
@@ -8414,11 +8414,6 @@
       <c r="E64" t="n">
         <v>100138</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>

--- a/artfynd/A 34151-2019 artfynd.xlsx
+++ b/artfynd/A 34151-2019 artfynd.xlsx
@@ -8399,7 +8399,7 @@
         <v>121864880</v>
       </c>
       <c r="B64" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8413,6 +8413,11 @@
       </c>
       <c r="E64" t="n">
         <v>100138</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>

--- a/artfynd/A 34151-2019 artfynd.xlsx
+++ b/artfynd/A 34151-2019 artfynd.xlsx
@@ -8399,7 +8399,7 @@
         <v>121864880</v>
       </c>
       <c r="B64" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>

--- a/artfynd/A 34151-2019 artfynd.xlsx
+++ b/artfynd/A 34151-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7330,10 +7330,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113995136</v>
+        <v>118024126</v>
       </c>
       <c r="B55" t="n">
-        <v>89787</v>
+        <v>97846</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7342,52 +7342,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hjortvägen, Srm</t>
+          <t>Bråtarna, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>608627</v>
+        <v>609043</v>
       </c>
       <c r="R55" t="n">
-        <v>6574058</v>
+        <v>6574157</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7411,12 +7408,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7432,19 +7439,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Peter Lantz</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bernt Andersson</t>
+          <t>Peter Lantz</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118024126</v>
+        <v>118024123</v>
       </c>
       <c r="B56" t="n">
         <v>97846</v>
@@ -7492,10 +7499,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609043</v>
+        <v>609012</v>
       </c>
       <c r="R56" t="n">
-        <v>6574157</v>
+        <v>6574164</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7527,7 +7534,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7537,7 +7544,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7565,7 +7572,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118024123</v>
+        <v>118024128</v>
       </c>
       <c r="B57" t="n">
         <v>97846</v>
@@ -7613,10 +7620,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609012</v>
+        <v>609052</v>
       </c>
       <c r="R57" t="n">
-        <v>6574164</v>
+        <v>6574161</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7648,7 +7655,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7658,7 +7665,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7686,7 +7693,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118024128</v>
+        <v>118024124</v>
       </c>
       <c r="B58" t="n">
         <v>97846</v>
@@ -7734,10 +7741,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>609052</v>
+        <v>609041</v>
       </c>
       <c r="R58" t="n">
-        <v>6574161</v>
+        <v>6574167</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7769,7 +7776,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7779,7 +7786,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7807,7 +7814,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118024124</v>
+        <v>118024125</v>
       </c>
       <c r="B59" t="n">
         <v>97846</v>
@@ -7855,10 +7862,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609041</v>
+        <v>609039</v>
       </c>
       <c r="R59" t="n">
-        <v>6574167</v>
+        <v>6574166</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7928,7 +7935,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118024125</v>
+        <v>118024122</v>
       </c>
       <c r="B60" t="n">
         <v>97846</v>
@@ -7976,7 +7983,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>609039</v>
+        <v>609017</v>
       </c>
       <c r="R60" t="n">
         <v>6574166</v>
@@ -8011,7 +8018,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8021,7 +8028,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8049,7 +8056,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118024122</v>
+        <v>118024127</v>
       </c>
       <c r="B61" t="n">
         <v>97846</v>
@@ -8083,24 +8090,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bråtarna, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609017</v>
+        <v>609051</v>
       </c>
       <c r="R61" t="n">
-        <v>6574166</v>
+        <v>6574160</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8132,7 +8131,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8142,7 +8141,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8151,7 +8150,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8170,10 +8168,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118024127</v>
+        <v>119178587</v>
       </c>
       <c r="B62" t="n">
-        <v>97846</v>
+        <v>57324</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8182,41 +8180,53 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bråtarna, Srm</t>
+          <t>Hjortvägen, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609051</v>
+        <v>608699</v>
       </c>
       <c r="R62" t="n">
-        <v>6574160</v>
+        <v>6574322</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8240,22 +8250,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8270,49 +8270,49 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Peter Lantz</t>
+          <t>Bernt Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Peter Lantz</t>
+          <t>Bernt Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119178587</v>
+        <v>121864880</v>
       </c>
       <c r="B63" t="n">
-        <v>57324</v>
+        <v>56594</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8321,26 +8321,30 @@
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hjortvägen, Srm</t>
+          <t>Bråtarna 6, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>608699</v>
+        <v>609010</v>
       </c>
       <c r="R63" t="n">
-        <v>6574322</v>
+        <v>6574278</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8364,12 +8368,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2024-12-22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2024-12-22</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8393,129 +8402,6 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>121864880</v>
-      </c>
-      <c r="B64" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Bråtarna 6, Srm</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>609010</v>
-      </c>
-      <c r="R64" t="n">
-        <v>6574278</v>
-      </c>
-      <c r="S64" t="n">
-        <v>50</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Strängnäs</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Länna</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2024-12-22</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2024-12-22</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Bernt Andersson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Bernt Andersson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
